--- a/02_DIA_inicio_2026_analisis_assets/rbd_9413_escuela-general-basica-santa-fe_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9413_escuela-general-basica-santa-fe_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E82B232-C841-4CC6-9391-17E86AFFF111}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{953DA0C6-D972-46DA-B7F5-007E069C77EF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74074540-0D50-46E1-9B1D-6992189F21C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E6EFD98-14E2-4978-B063-D4E46F0A9E8E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68AF308F-0119-4C85-9101-5A912B323A5D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{930E5C0C-265D-4DA4-9106-01CF26BBF159}"/>
 </file>